--- a/output/pdf_financials_xlsx/HPQ.xlsx
+++ b/output/pdf_financials_xlsx/HPQ.xlsx
@@ -2320,40 +2320,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.247542</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.062822</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.028159</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.054335</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.177585</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.472393</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.314103</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.32055</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.07761800000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.888282</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.672696</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.143902</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.597404</v>
@@ -2424,40 +2424,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.247542</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.062822</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.028159</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.054335</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.177585</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.472393</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.314103</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.32055</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.07761800000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.722</v>
+        <v>2.610282</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.666</v>
+        <v>3.338696</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.710403</v>
+        <v>1.854305</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.273897</v>
@@ -3054,34 +3054,34 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.649964</v>
+        <v>0.6218050000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.481479</v>
+        <v>0.427144</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.875646</v>
+        <v>0.698061</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.497544</v>
+        <v>3.025151</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.843366</v>
+        <v>2.529263</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.022683</v>
+        <v>2.702133</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.294572</v>
+        <v>2.216954</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.241648</v>
+        <v>0.353366</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.744906</v>
+        <v>1.07221</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.84139</v>
+        <v>3.697488</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.952052</v>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -30903,7 +30903,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">

--- a/output/pdf_financials_xlsx/HPQ.xlsx
+++ b/output/pdf_financials_xlsx/HPQ.xlsx
@@ -2018,16 +2018,16 @@
         <v>0.234021</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.611023</v>
+        <v>0.613599</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.685724</v>
+        <v>0.696124</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.290489</v>
+        <v>0.301889</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.159199</v>
+        <v>0.172053</v>
       </c>
     </row>
     <row r="29">
@@ -2074,16 +2074,16 @@
         <v>-6.097245</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-8.473112</v>
+        <v>-8.470535999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-15.358605</v>
+        <v>-15.348205</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.700759</v>
+        <v>-7.689359</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>35.70236</v>
+        <v>35.715214</v>
       </c>
     </row>
     <row r="30">
@@ -5820,22 +5820,22 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.038857</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.234021</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.613599</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.696124</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.301889</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.172053</v>
       </c>
     </row>
     <row r="101">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -31817,7 +31817,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -35105,7 +35109,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -36222,7 +36226,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -39970,7 +39978,11 @@
           <t>Addition to intangible assets</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -44701,7 +44713,11 @@
           <t>Addition to intangible assets (4</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HPQ.xlsx
+++ b/output/pdf_financials_xlsx/HPQ.xlsx
@@ -6652,10 +6652,10 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-2.987318</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-3.735127</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
@@ -31455,7 +31455,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -39163,7 +39167,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -51084,7 +51092,11 @@
           <t>Issuance of units by a flow-through private placement</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E489" s="5" t="n">
         <v>0.25</v>
       </c>
